--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,141 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123324318</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101755</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Prästbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>606092</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6991377</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_1295</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt längsmed grusväg</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299484</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101755</v>
+        <v>101758</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299484</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101758</v>
+        <v>101760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299484</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101760</v>
+        <v>101766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299484</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101769</v>
+        <v>101786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299484</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101786</v>
+        <v>101804</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123299484</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101804</v>
+        <v>101806</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60060-2024 artfynd.xlsx
+++ b/artfynd/A 60060-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>123324318</v>
       </c>
       <c r="B3" t="n">
-        <v>101806</v>
+        <v>101381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
